--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47C.xlsx
@@ -103,28 +103,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>492C9A9537DE03611FEFC555130F1780</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de julio del 2022 al 30 de septiembre del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no publico información respecto a transparencia proactiva debido a que no se generó política en referencia a este tema.</t>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>52FE2308532C398ED0CC3FE2FAA2BCCF</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de julio del 2023 al 30 de septiembre del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, de acuerdo al  artículo 2, fracción VIII, artículo 25, fracción XII y artículo 50 de la LEY DE TRANSPARENCIA Y ACCESO A LA INFORMACIÓN PÚBLICA DEL ESTADO DE TLAXCALA, motivo por el cual no publico información respecto a transparencia proactiva debido a que no se generó política en referencia a este tema.</t>
   </si>
 </sst>
 </file>
@@ -520,7 +520,7 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -528,7 +528,7 @@
     <col min="6" max="6" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="206.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
@@ -661,22 +661,22 @@
     </row>
     <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>35</v>
